--- a/04_3일차_팀프로젝트_실습기획서.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\workspace\00aicamp\Day03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\workspace\00aicamp\13_6_localhub\ssafy_seoul_13_06_vibe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFD7A4A-892A-46CF-B6AE-065FFA9EDE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7FEC14-3E66-4113-9072-C2944A59226D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="3915" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="390">
   <si>
     <t>실습 소재</t>
   </si>
@@ -9490,6 +9490,1327 @@
   <si>
     <t>납기 내 필수기능 100% 구현 + 선택기능 2개 배포 + 배포 URL 정상 동작</t>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요구사항</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확정</t>
+    </r>
+  </si>
+  <si>
+    <t>팀전체</t>
+  </si>
+  <si>
+    <r>
+      <t>권역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MVP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정의</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카테고리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선정</t>
+    </r>
+  </si>
+  <si>
+    <t>FE</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스키마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (SQLite)</t>
+    </r>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명세서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좌표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+  </si>
+  <si>
+    <t>FE/BE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>레이아웃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라우팅</t>
+    </r>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게시판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게시판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연동</t>
+    </r>
+  </si>
+  <si>
+    <t>예정</t>
+  </si>
+  <si>
+    <r>
+      <t>챗봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>챗봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> UI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위젯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카테고리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>위치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Netlify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Render </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>게시판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챗봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반응형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>기능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명세서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>출처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PPT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제작</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리허설</t>
+    </r>
+  </si>
+  <si>
+    <t>팀전체</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
   </si>
 </sst>
 </file>
@@ -9499,7 +10820,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;Day &quot;0"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9870,6 +11191,13 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -9969,7 +11297,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -10066,11 +11394,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -10144,6 +11512,43 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -10190,13 +11595,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10211,29 +11616,20 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10271,62 +11667,105 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF028090"/>
+          <bgColor rgb="FF028090"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -10616,10 +12055,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="33"/>
+      <c r="C2" s="46"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="12" t="s">
@@ -10654,10 +12093,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="30"/>
+      <c r="C9" s="43"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -10708,28 +12147,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="32"/>
+      <c r="C17" s="45"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="35"/>
+      <c r="C18" s="48"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="28"/>
+      <c r="C19" s="41"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="28"/>
+      <c r="C20" s="41"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -10763,13 +12202,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -10861,46 +12300,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="30"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="43"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10934,22 +12373,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="30" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
     </row>
     <row r="3" spans="2:15" ht="28.35" customHeight="1">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="30"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" spans="2:15" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -10981,31 +12420,31 @@
       <c r="B6" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="K6" s="73" t="s">
+      <c r="K6" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L6" s="73" t="s">
+      <c r="L6" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="M6" s="73" t="s">
+      <c r="M6" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="N6" s="73" t="s">
+      <c r="N6" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="73" t="s">
+      <c r="O6" s="29" t="s">
         <v>153</v>
       </c>
     </row>
@@ -11013,31 +12452,31 @@
       <c r="B7" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="K7" s="73" t="s">
+      <c r="K7" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L7" s="73" t="s">
+      <c r="L7" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="M7" s="73" t="s">
+      <c r="M7" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="N7" s="73" t="s">
+      <c r="N7" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="O7" s="73" t="s">
+      <c r="O7" s="29" t="s">
         <v>156</v>
       </c>
     </row>
@@ -11045,31 +12484,31 @@
       <c r="B8" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C8" s="73" t="s">
+      <c r="C8" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="73" t="s">
+      <c r="D8" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="73" t="s">
+      <c r="E8" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="K8" s="73" t="s">
+      <c r="K8" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L8" s="73" t="s">
+      <c r="L8" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="M8" s="73" t="s">
+      <c r="M8" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="N8" s="73" t="s">
+      <c r="N8" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="O8" s="73" t="s">
+      <c r="O8" s="29" t="s">
         <v>160</v>
       </c>
     </row>
@@ -11077,31 +12516,31 @@
       <c r="B9" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="D9" s="73" t="s">
+      <c r="D9" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="73" t="s">
+      <c r="F9" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="K9" s="73" t="s">
+      <c r="K9" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L9" s="73" t="s">
+      <c r="L9" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="M9" s="73" t="s">
+      <c r="M9" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="N9" s="73" t="s">
+      <c r="N9" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="O9" s="73" t="s">
+      <c r="O9" s="29" t="s">
         <v>164</v>
       </c>
     </row>
@@ -11109,31 +12548,31 @@
       <c r="B10" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="D10" s="73" t="s">
+      <c r="D10" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="E10" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="K10" s="73" t="s">
+      <c r="K10" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L10" s="73" t="s">
+      <c r="L10" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="M10" s="73" t="s">
+      <c r="M10" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="N10" s="73" t="s">
+      <c r="N10" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="O10" s="73" t="s">
+      <c r="O10" s="29" t="s">
         <v>168</v>
       </c>
     </row>
@@ -11141,31 +12580,31 @@
       <c r="B11" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="73" t="s">
+      <c r="D11" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="E11" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F11" s="73" t="s">
+      <c r="F11" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="K11" s="73" t="s">
+      <c r="K11" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L11" s="73" t="s">
+      <c r="L11" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="M11" s="73" t="s">
+      <c r="M11" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="N11" s="73" t="s">
+      <c r="N11" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="O11" s="73" t="s">
+      <c r="O11" s="29" t="s">
         <v>172</v>
       </c>
     </row>
@@ -11173,31 +12612,31 @@
       <c r="B12" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="D12" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="E12" s="73" t="s">
+      <c r="E12" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="F12" s="73" t="s">
+      <c r="F12" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="K12" s="73" t="s">
+      <c r="K12" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L12" s="73" t="s">
+      <c r="L12" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="M12" s="73" t="s">
+      <c r="M12" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="N12" s="73" t="s">
+      <c r="N12" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="O12" s="73" t="s">
+      <c r="O12" s="29" t="s">
         <v>176</v>
       </c>
     </row>
@@ -11205,31 +12644,31 @@
       <c r="B13" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="K13" s="73" t="s">
+      <c r="K13" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L13" s="73" t="s">
+      <c r="L13" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="M13" s="73" t="s">
+      <c r="M13" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="N13" s="73" t="s">
+      <c r="N13" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="O13" s="73" t="s">
+      <c r="O13" s="29" t="s">
         <v>180</v>
       </c>
     </row>
@@ -11237,31 +12676,31 @@
       <c r="B14" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="E14" s="73" t="s">
+      <c r="E14" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="K14" s="73" t="s">
+      <c r="K14" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L14" s="73" t="s">
+      <c r="L14" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="M14" s="73" t="s">
+      <c r="M14" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="N14" s="73" t="s">
+      <c r="N14" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="O14" s="73" t="s">
+      <c r="O14" s="29" t="s">
         <v>184</v>
       </c>
     </row>
@@ -11269,31 +12708,31 @@
       <c r="B15" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="D15" s="73" t="s">
+      <c r="D15" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="E15" s="73" t="s">
+      <c r="E15" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="K15" s="73" t="s">
+      <c r="K15" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L15" s="73" t="s">
+      <c r="L15" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="M15" s="73" t="s">
+      <c r="M15" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="N15" s="73" t="s">
+      <c r="N15" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="O15" s="73" t="s">
+      <c r="O15" s="29" t="s">
         <v>188</v>
       </c>
     </row>
@@ -11301,31 +12740,31 @@
       <c r="B16" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C16" s="73" t="s">
+      <c r="C16" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="73" t="s">
+      <c r="D16" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="E16" s="73" t="s">
+      <c r="E16" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="73" t="s">
+      <c r="F16" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="K16" s="73" t="s">
+      <c r="K16" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L16" s="73" t="s">
+      <c r="L16" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="M16" s="73" t="s">
+      <c r="M16" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="N16" s="73" t="s">
+      <c r="N16" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="O16" s="73" t="s">
+      <c r="O16" s="29" t="s">
         <v>192</v>
       </c>
     </row>
@@ -11333,31 +12772,31 @@
       <c r="B17" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C17" s="73" t="s">
+      <c r="C17" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="F17" s="73" t="s">
+      <c r="F17" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="K17" s="73" t="s">
+      <c r="K17" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L17" s="73" t="s">
+      <c r="L17" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="M17" s="73" t="s">
+      <c r="M17" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="N17" s="73" t="s">
+      <c r="N17" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="O17" s="73" t="s">
+      <c r="O17" s="29" t="s">
         <v>196</v>
       </c>
     </row>
@@ -11365,31 +12804,31 @@
       <c r="B18" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C18" s="73" t="s">
+      <c r="C18" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="D18" s="73" t="s">
+      <c r="D18" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E18" s="73" t="s">
+      <c r="E18" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="F18" s="73" t="s">
+      <c r="F18" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="K18" s="73" t="s">
+      <c r="K18" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L18" s="73" t="s">
+      <c r="L18" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="M18" s="73" t="s">
+      <c r="M18" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="N18" s="73" t="s">
+      <c r="N18" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="O18" s="73" t="s">
+      <c r="O18" s="29" t="s">
         <v>200</v>
       </c>
     </row>
@@ -11397,818 +12836,818 @@
       <c r="B19" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C19" s="73" t="s">
+      <c r="C19" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="D19" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="K19" s="73" t="s">
+      <c r="K19" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L19" s="73" t="s">
+      <c r="L19" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="M19" s="73" t="s">
+      <c r="M19" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="N19" s="73" t="s">
+      <c r="N19" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="O19" s="73" t="s">
+      <c r="O19" s="29" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="30" customHeight="1">
       <c r="B20" s="3"/>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="73" t="s">
+      <c r="D20" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="E20" s="73" t="s">
+      <c r="E20" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="F20" s="73" t="s">
+      <c r="F20" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="K20" s="73" t="s">
+      <c r="K20" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L20" s="73" t="s">
+      <c r="L20" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="73" t="s">
+      <c r="M20" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="N20" s="73" t="s">
+      <c r="N20" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="O20" s="73" t="s">
+      <c r="O20" s="29" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="30" customHeight="1">
       <c r="B21" s="3"/>
-      <c r="C21" s="73" t="s">
+      <c r="C21" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D21" s="73" t="s">
+      <c r="D21" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="F21" s="73" t="s">
+      <c r="F21" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="K21" s="73" t="s">
+      <c r="K21" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L21" s="73" t="s">
+      <c r="L21" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="M21" s="73" t="s">
+      <c r="M21" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="N21" s="73" t="s">
+      <c r="N21" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="O21" s="73" t="s">
+      <c r="O21" s="29" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="30" customHeight="1">
       <c r="B22" s="3"/>
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D22" s="73" t="s">
+      <c r="D22" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="E22" s="73" t="s">
+      <c r="E22" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="F22" s="73" t="s">
+      <c r="F22" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="K22" s="73" t="s">
+      <c r="K22" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L22" s="73" t="s">
+      <c r="L22" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="M22" s="73" t="s">
+      <c r="M22" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="N22" s="73" t="s">
+      <c r="N22" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="O22" s="73" t="s">
+      <c r="O22" s="29" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="30" customHeight="1">
       <c r="B23" s="3"/>
-      <c r="C23" s="73" t="s">
+      <c r="C23" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="D23" s="73" t="s">
+      <c r="D23" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="E23" s="73" t="s">
+      <c r="E23" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="F23" s="73" t="s">
+      <c r="F23" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="K23" s="73" t="s">
+      <c r="K23" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="L23" s="73" t="s">
+      <c r="L23" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="M23" s="73" t="s">
+      <c r="M23" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="N23" s="73" t="s">
+      <c r="N23" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="O23" s="73" t="s">
+      <c r="O23" s="29" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="24" spans="2:15" ht="60">
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="D24" s="73" t="s">
+      <c r="D24" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="E24" s="73" t="s">
+      <c r="E24" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F24" s="73" t="s">
+      <c r="F24" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="K24" s="73" t="s">
+      <c r="K24" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L24" s="73" t="s">
+      <c r="L24" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="M24" s="73" t="s">
+      <c r="M24" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="N24" s="73" t="s">
+      <c r="N24" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O24" s="73" t="s">
+      <c r="O24" s="29" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="25" spans="2:15" ht="45">
-      <c r="C25" s="73" t="s">
+      <c r="C25" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F25" s="73" t="s">
+      <c r="F25" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="K25" s="73" t="s">
+      <c r="K25" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L25" s="73" t="s">
+      <c r="L25" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="M25" s="73" t="s">
+      <c r="M25" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="N25" s="73" t="s">
+      <c r="N25" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O25" s="73" t="s">
+      <c r="O25" s="29" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="26" spans="2:15" ht="45">
-      <c r="C26" s="73" t="s">
+      <c r="C26" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="D26" s="73" t="s">
+      <c r="D26" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="E26" s="73" t="s">
+      <c r="E26" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F26" s="73" t="s">
+      <c r="F26" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="K26" s="73" t="s">
+      <c r="K26" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L26" s="73" t="s">
+      <c r="L26" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="M26" s="73" t="s">
+      <c r="M26" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="N26" s="73" t="s">
+      <c r="N26" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O26" s="73" t="s">
+      <c r="O26" s="29" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="27" spans="2:15" ht="45">
-      <c r="C27" s="73" t="s">
+      <c r="C27" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="D27" s="73" t="s">
+      <c r="D27" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="E27" s="73" t="s">
+      <c r="E27" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F27" s="73" t="s">
+      <c r="F27" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="K27" s="73" t="s">
+      <c r="K27" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L27" s="73" t="s">
+      <c r="L27" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="M27" s="73" t="s">
+      <c r="M27" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="N27" s="73" t="s">
+      <c r="N27" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O27" s="73" t="s">
+      <c r="O27" s="29" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="28" spans="2:15" ht="30">
-      <c r="C28" s="73" t="s">
+      <c r="C28" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="D28" s="73" t="s">
+      <c r="D28" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="E28" s="73" t="s">
+      <c r="E28" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F28" s="73" t="s">
+      <c r="F28" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="K28" s="73" t="s">
+      <c r="K28" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L28" s="73" t="s">
+      <c r="L28" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="M28" s="73" t="s">
+      <c r="M28" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="N28" s="73" t="s">
+      <c r="N28" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O28" s="73" t="s">
+      <c r="O28" s="29" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="45">
-      <c r="C29" s="73" t="s">
+      <c r="C29" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="E29" s="73" t="s">
+      <c r="E29" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F29" s="73" t="s">
+      <c r="F29" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="K29" s="73" t="s">
+      <c r="K29" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L29" s="73" t="s">
+      <c r="L29" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="M29" s="73" t="s">
+      <c r="M29" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="N29" s="73" t="s">
+      <c r="N29" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O29" s="73" t="s">
+      <c r="O29" s="29" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="30">
-      <c r="C30" s="73" t="s">
+      <c r="C30" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="D30" s="73" t="s">
+      <c r="D30" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="E30" s="73" t="s">
+      <c r="E30" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F30" s="73" t="s">
+      <c r="F30" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="K30" s="73" t="s">
+      <c r="K30" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L30" s="73" t="s">
+      <c r="L30" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="M30" s="73" t="s">
+      <c r="M30" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="N30" s="73" t="s">
+      <c r="N30" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O30" s="73" t="s">
+      <c r="O30" s="29" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="31" spans="2:15" ht="45">
-      <c r="C31" s="73" t="s">
+      <c r="C31" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="D31" s="73" t="s">
+      <c r="D31" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="E31" s="73" t="s">
+      <c r="E31" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F31" s="73" t="s">
+      <c r="F31" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="K31" s="73" t="s">
+      <c r="K31" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L31" s="73" t="s">
+      <c r="L31" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="M31" s="73" t="s">
+      <c r="M31" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="N31" s="73" t="s">
+      <c r="N31" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O31" s="73" t="s">
+      <c r="O31" s="29" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="75">
-      <c r="C32" s="73" t="s">
+      <c r="C32" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="D32" s="73" t="s">
+      <c r="D32" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="E32" s="73" t="s">
+      <c r="E32" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F32" s="73" t="s">
+      <c r="F32" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="K32" s="73" t="s">
+      <c r="K32" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="L32" s="73" t="s">
+      <c r="L32" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="M32" s="73" t="s">
+      <c r="M32" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="N32" s="73" t="s">
+      <c r="N32" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O32" s="73" t="s">
+      <c r="O32" s="29" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="33" spans="3:15" ht="105">
-      <c r="C33" s="73" t="s">
+      <c r="C33" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="D33" s="74" t="s">
+      <c r="D33" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="E33" s="73" t="s">
+      <c r="E33" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="F33" s="73" t="s">
+      <c r="F33" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="K33" s="73" t="s">
+      <c r="K33" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L33" s="73" t="s">
+      <c r="L33" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="M33" s="74" t="s">
+      <c r="M33" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="N33" s="73" t="s">
+      <c r="N33" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="O33" s="73" t="s">
+      <c r="O33" s="29" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="34" spans="3:15" ht="75">
-      <c r="C34" s="73" t="s">
+      <c r="C34" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="D34" s="73" t="s">
+      <c r="D34" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="E34" s="73" t="s">
+      <c r="E34" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="73" t="s">
+      <c r="F34" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="K34" s="73" t="s">
+      <c r="K34" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L34" s="73" t="s">
+      <c r="L34" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="M34" s="73" t="s">
+      <c r="M34" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="N34" s="73" t="s">
+      <c r="N34" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="O34" s="73" t="s">
+      <c r="O34" s="29" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35" spans="3:15" ht="75">
-      <c r="C35" s="73" t="s">
+      <c r="C35" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="D35" s="73" t="s">
+      <c r="D35" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="E35" s="73" t="s">
+      <c r="E35" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="F35" s="73" t="s">
+      <c r="F35" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="K35" s="73" t="s">
+      <c r="K35" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L35" s="73" t="s">
+      <c r="L35" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="M35" s="73" t="s">
+      <c r="M35" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="N35" s="73" t="s">
+      <c r="N35" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="O35" s="73" t="s">
+      <c r="O35" s="29" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="36" spans="3:15" ht="60">
-      <c r="C36" s="73" t="s">
+      <c r="C36" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="D36" s="73" t="s">
+      <c r="D36" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="E36" s="73" t="s">
+      <c r="E36" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="F36" s="73" t="s">
+      <c r="F36" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="K36" s="73" t="s">
+      <c r="K36" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L36" s="73" t="s">
+      <c r="L36" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="M36" s="73" t="s">
+      <c r="M36" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="N36" s="73" t="s">
+      <c r="N36" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="O36" s="73" t="s">
+      <c r="O36" s="29" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="37" spans="3:15" ht="105">
-      <c r="C37" s="73" t="s">
+      <c r="C37" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="D37" s="73" t="s">
+      <c r="D37" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="E37" s="73" t="s">
+      <c r="E37" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F37" s="73" t="s">
+      <c r="F37" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="K37" s="73" t="s">
+      <c r="K37" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L37" s="73" t="s">
+      <c r="L37" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="M37" s="73" t="s">
+      <c r="M37" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="N37" s="73" t="s">
+      <c r="N37" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="O37" s="73" t="s">
+      <c r="O37" s="29" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="38" spans="3:15" ht="135">
-      <c r="C38" s="73" t="s">
+      <c r="C38" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="D38" s="74" t="s">
+      <c r="D38" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="E38" s="73" t="s">
+      <c r="E38" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F38" s="73" t="s">
+      <c r="F38" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="K38" s="73" t="s">
+      <c r="K38" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L38" s="73" t="s">
+      <c r="L38" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="M38" s="74" t="s">
+      <c r="M38" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="N38" s="73" t="s">
+      <c r="N38" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="O38" s="73" t="s">
+      <c r="O38" s="29" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="39" spans="3:15" ht="75">
-      <c r="C39" s="73" t="s">
+      <c r="C39" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="D39" s="73" t="s">
+      <c r="D39" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="F39" s="73" t="s">
+      <c r="F39" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="K39" s="73" t="s">
+      <c r="K39" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L39" s="73" t="s">
+      <c r="L39" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="M39" s="73" t="s">
+      <c r="M39" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="N39" s="73" t="s">
+      <c r="N39" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="O39" s="73" t="s">
+      <c r="O39" s="29" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="40" spans="3:15" ht="105">
-      <c r="C40" s="73" t="s">
+      <c r="C40" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="D40" s="74" t="s">
+      <c r="D40" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="E40" s="73" t="s">
+      <c r="E40" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="F40" s="73" t="s">
+      <c r="F40" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="K40" s="73" t="s">
+      <c r="K40" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L40" s="73" t="s">
+      <c r="L40" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="M40" s="74" t="s">
+      <c r="M40" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="N40" s="73" t="s">
+      <c r="N40" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="O40" s="73" t="s">
+      <c r="O40" s="29" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="41" spans="3:15" ht="90">
-      <c r="C41" s="73" t="s">
+      <c r="C41" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="D41" s="74" t="s">
+      <c r="D41" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="E41" s="73" t="s">
+      <c r="E41" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="F41" s="73" t="s">
+      <c r="F41" s="29" t="s">
         <v>276</v>
       </c>
-      <c r="K41" s="73" t="s">
+      <c r="K41" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L41" s="73" t="s">
+      <c r="L41" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="M41" s="74" t="s">
+      <c r="M41" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="N41" s="73" t="s">
+      <c r="N41" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="O41" s="73" t="s">
+      <c r="O41" s="29" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="42" spans="3:15" ht="75">
-      <c r="C42" s="73" t="s">
+      <c r="C42" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="D42" s="73" t="s">
+      <c r="D42" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="E42" s="73" t="s">
+      <c r="E42" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="F42" s="73" t="s">
+      <c r="F42" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="K42" s="73" t="s">
+      <c r="K42" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L42" s="73" t="s">
+      <c r="L42" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="M42" s="73" t="s">
+      <c r="M42" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="N42" s="73" t="s">
+      <c r="N42" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="O42" s="73" t="s">
+      <c r="O42" s="29" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="43" spans="3:15" ht="105">
-      <c r="C43" s="73" t="s">
+      <c r="C43" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="D43" s="73" t="s">
+      <c r="D43" s="29" t="s">
         <v>281</v>
       </c>
-      <c r="E43" s="73" t="s">
+      <c r="E43" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="F43" s="73" t="s">
+      <c r="F43" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="K43" s="73" t="s">
+      <c r="K43" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L43" s="73" t="s">
+      <c r="L43" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="M43" s="73" t="s">
+      <c r="M43" s="29" t="s">
         <v>281</v>
       </c>
-      <c r="N43" s="73" t="s">
+      <c r="N43" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="O43" s="73" t="s">
+      <c r="O43" s="29" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="44" spans="3:15" ht="45">
-      <c r="C44" s="73" t="s">
+      <c r="C44" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="D44" s="73" t="s">
+      <c r="D44" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="E44" s="73" t="s">
+      <c r="E44" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="F44" s="73" t="s">
+      <c r="F44" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="K44" s="73" t="s">
+      <c r="K44" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L44" s="73" t="s">
+      <c r="L44" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="M44" s="73" t="s">
+      <c r="M44" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="N44" s="73" t="s">
+      <c r="N44" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="O44" s="73" t="s">
+      <c r="O44" s="29" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="45" spans="3:15" ht="120">
-      <c r="C45" s="73" t="s">
+      <c r="C45" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="73" t="s">
+      <c r="D45" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="E45" s="73" t="s">
+      <c r="E45" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="F45" s="73" t="s">
+      <c r="F45" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="K45" s="73" t="s">
+      <c r="K45" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L45" s="73" t="s">
+      <c r="L45" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="M45" s="73" t="s">
+      <c r="M45" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="N45" s="73" t="s">
+      <c r="N45" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="O45" s="73" t="s">
+      <c r="O45" s="29" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="46" spans="3:15" ht="105">
-      <c r="C46" s="73" t="s">
+      <c r="C46" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="D46" s="73" t="s">
+      <c r="D46" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="E46" s="73" t="s">
+      <c r="E46" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="F46" s="73" t="s">
+      <c r="F46" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="K46" s="73" t="s">
+      <c r="K46" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="L46" s="73" t="s">
+      <c r="L46" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="M46" s="73" t="s">
+      <c r="M46" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="N46" s="73" t="s">
+      <c r="N46" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="O46" s="73" t="s">
+      <c r="O46" s="29" t="s">
         <v>292</v>
       </c>
     </row>
@@ -12246,274 +13685,274 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="30"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="43"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="43"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="77" t="s">
+      <c r="F5" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="33" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C6" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="35">
         <v>2</v>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="36">
         <v>5</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="36">
         <v>5</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="37">
         <f t="shared" ref="G6:G14" si="0">IF(OR(E6="",F6=""),"",E6*F6*2)</f>
         <v>50</v>
       </c>
-      <c r="H6" s="81" t="s">
+      <c r="H6" s="37" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="34" t="s">
         <v>223</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="35">
         <v>2</v>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="36">
         <v>5</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="36">
         <v>3</v>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="37">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="37" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="78" t="s">
+      <c r="C8" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="D8" s="79">
+      <c r="D8" s="35">
         <v>2</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="36">
         <v>5</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="36">
         <v>4</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="37">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H8" s="81" t="s">
+      <c r="H8" s="37" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="79">
+      <c r="D9" s="35">
         <v>4</v>
       </c>
-      <c r="E9" s="80">
+      <c r="E9" s="36">
         <v>2</v>
       </c>
-      <c r="F9" s="80">
+      <c r="F9" s="36">
         <v>5</v>
       </c>
-      <c r="G9" s="81">
+      <c r="G9" s="37">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H9" s="81" t="s">
+      <c r="H9" s="37" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="78" t="s">
+      <c r="C10" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="35">
         <v>2</v>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="36">
         <v>5</v>
       </c>
-      <c r="F10" s="80">
+      <c r="F10" s="36">
         <v>4</v>
       </c>
-      <c r="G10" s="81">
+      <c r="G10" s="37">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H10" s="81" t="s">
+      <c r="H10" s="37" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="35">
         <v>5</v>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="36">
         <v>1</v>
       </c>
-      <c r="F11" s="80">
+      <c r="F11" s="36">
         <v>3</v>
       </c>
-      <c r="G11" s="81">
+      <c r="G11" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H11" s="81" t="s">
+      <c r="H11" s="37" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="C12" s="78" t="s">
+      <c r="C12" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="D12" s="79">
+      <c r="D12" s="35">
         <v>3</v>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="36">
         <v>4</v>
       </c>
-      <c r="F12" s="80">
+      <c r="F12" s="36">
         <v>3</v>
       </c>
-      <c r="G12" s="81">
+      <c r="G12" s="37">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H12" s="81" t="s">
+      <c r="H12" s="37" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="35">
         <v>1</v>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="36">
         <v>5</v>
       </c>
-      <c r="F13" s="80">
+      <c r="F13" s="36">
         <v>4</v>
       </c>
-      <c r="G13" s="81">
+      <c r="G13" s="37">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H13" s="81" t="s">
+      <c r="H13" s="37" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="14" spans="2:8" s="26" customFormat="1" ht="33.75" customHeight="1">
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="D14" s="79">
+      <c r="D14" s="35">
         <v>2</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="36">
         <v>5</v>
       </c>
-      <c r="F14" s="80">
+      <c r="F14" s="36">
         <v>5</v>
       </c>
-      <c r="G14" s="81">
+      <c r="G14" s="37">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="H14" s="81" t="s">
+      <c r="H14" s="37" t="s">
         <v>306</v>
       </c>
     </row>
@@ -12521,14 +13960,14 @@
       <c r="B16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="32"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12539,7 +13978,7 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="G6:G14">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>AND(G6&lt;&gt;"",G6&gt;=32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12573,38 +14012,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="G2" s="72" t="s">
+      <c r="C2" s="52"/>
+      <c r="G2" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="J2" s="28" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="18" customHeight="1">
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="G3" s="74" t="s">
+      <c r="C3" s="43"/>
+      <c r="G3" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H3" s="74" t="s">
+      <c r="H3" s="30" t="s">
         <v>343</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="J3" s="73" t="s">
+      <c r="J3" s="29" t="s">
         <v>313</v>
       </c>
     </row>
@@ -12615,10 +14054,10 @@
       <c r="C4" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="2:10" ht="30" customHeight="1">
       <c r="B5" s="1" t="s">
@@ -12627,10 +14066,10 @@
       <c r="C5" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="2:10" ht="30" customHeight="1">
       <c r="B6" s="1" t="s">
@@ -12639,10 +14078,10 @@
       <c r="C6" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
     </row>
     <row r="7" spans="2:10" ht="30" customHeight="1">
       <c r="B7" s="1" t="s">
@@ -12651,279 +14090,287 @@
       <c r="C7" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="I7" s="73" t="s">
+      <c r="I7" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="J7" s="73" t="s">
+      <c r="J7" s="29" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="60">
-      <c r="G8" s="74" t="s">
+    <row r="8" spans="2:10" ht="30">
+      <c r="G8" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H8" s="74" t="s">
+      <c r="H8" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="I8" s="73" t="s">
+      <c r="I8" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="J8" s="73" t="s">
+      <c r="J8" s="29" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15" customHeight="1">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="G9" s="74" t="s">
+      <c r="C9" s="66"/>
+      <c r="G9" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H9" s="74" t="s">
+      <c r="H9" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="I9" s="73" t="s">
+      <c r="I9" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="J9" s="73" t="s">
+      <c r="J9" s="29" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="G10" s="74" t="s">
+      <c r="C10" s="48"/>
+      <c r="G10" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H10" s="74" t="s">
+      <c r="H10" s="30" t="s">
         <v>321</v>
       </c>
-      <c r="I10" s="73" t="s">
+      <c r="I10" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="J10" s="73" t="s">
+      <c r="J10" s="29" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="69" t="s">
         <v>345</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="G11" s="74" t="s">
+      <c r="C11" s="48"/>
+      <c r="G11" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H11" s="74" t="s">
+      <c r="H11" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="I11" s="73" t="s">
+      <c r="I11" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="J11" s="73" t="s">
+      <c r="J11" s="29" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="47" t="s">
         <v>347</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="G12" s="74" t="s">
+      <c r="C12" s="48"/>
+      <c r="G12" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H12" s="84" t="s">
+      <c r="H12" s="38" t="s">
         <v>341</v>
       </c>
-      <c r="I12" s="73" t="s">
+      <c r="I12" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="J12" s="73" t="s">
+      <c r="J12" s="29" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="47" t="s">
         <v>346</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="G13" s="74" t="s">
+      <c r="C13" s="48"/>
+      <c r="G13" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H13" s="74" t="s">
+      <c r="H13" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="I13" s="73" t="s">
+      <c r="I13" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="J13" s="73" t="s">
+      <c r="J13" s="29" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="G14" s="74" t="s">
+      <c r="B14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="G14" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H14" s="74" t="s">
+      <c r="H14" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="I14" s="73" t="s">
+      <c r="I14" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="J14" s="73" t="s">
+      <c r="J14" s="29" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="60">
-      <c r="G15" s="74" t="s">
+    <row r="15" spans="2:10" ht="30">
+      <c r="G15" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H15" s="74" t="s">
+      <c r="H15" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="I15" s="73" t="s">
+      <c r="I15" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="J15" s="73" t="s">
+      <c r="J15" s="29" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="G16" s="74" t="s">
+      <c r="C16" s="64"/>
+      <c r="G16" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H16" s="74" t="s">
+      <c r="H16" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="I16" s="73" t="s">
+      <c r="I16" s="29" t="s">
         <v>335</v>
       </c>
-      <c r="J16" s="73" t="s">
+      <c r="J16" s="29" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="60" t="s">
         <v>351</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="G17" s="74" t="s">
+      <c r="C17" s="48"/>
+      <c r="G17" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H17" s="74" t="s">
+      <c r="H17" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="I17" s="73" t="s">
+      <c r="I17" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="J17" s="73" t="s">
+      <c r="J17" s="29" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="60" t="s">
         <v>354</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="G18" s="74" t="s">
+      <c r="C18" s="48"/>
+      <c r="G18" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="H18" s="74" t="s">
+      <c r="H18" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="I18" s="73" t="s">
+      <c r="I18" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="J18" s="73" t="s">
+      <c r="J18" s="29" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="48"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="72" t="s">
+      <c r="H20" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="I20" s="72" t="s">
+      <c r="I20" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="J20" s="73"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="G21" s="74" t="s">
+      <c r="C21" s="62"/>
+      <c r="G21" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="H21" s="84" t="s">
+      <c r="H21" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="I21" s="87" t="s">
+      <c r="I21" s="39" t="s">
         <v>350</v>
       </c>
-      <c r="J21" s="73"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="67" t="s">
         <v>357</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="G22" s="74" t="s">
+      <c r="C22" s="48"/>
+      <c r="G22" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="H22" s="84" t="s">
+      <c r="H22" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="I22" s="87" t="s">
+      <c r="I22" s="39" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="60" t="s">
         <v>358</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="G23" s="74" t="s">
+      <c r="C23" s="48"/>
+      <c r="G23" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="H23" s="84" t="s">
+      <c r="H23" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="I23" s="87" t="s">
+      <c r="I23" s="39" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="24" spans="2:10" ht="25.5" customHeight="1">
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
@@ -12932,14 +14379,6 @@
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12952,7 +14391,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B2:M28"/>
+  <dimension ref="B2:M39"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -12969,36 +14408,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="30"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="43"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="11" t="s">
@@ -13042,17 +14481,30 @@
       <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="str">
-        <f t="shared" ref="H5:H18" si="0">IF(OR(F5="",G5=""),"",G5-F5+1)</f>
-        <v/>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="C5" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="E5" s="86" t="s">
+        <v>364</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="86" t="s">
+        <v>389</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -13061,17 +14513,30 @@
       <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="C6" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="87" t="s">
+        <v>365</v>
+      </c>
+      <c r="E6" s="86" t="s">
+        <v>364</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="86" t="s">
+        <v>389</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -13080,17 +14545,30 @@
       <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="C7" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="87" t="s">
+        <v>366</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -13099,17 +14577,30 @@
       <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="C8" s="86" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -13118,17 +14609,30 @@
       <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="C9" s="86" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -13137,17 +14641,30 @@
       <c r="B10" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="C10" s="86" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="87" t="s">
+        <v>371</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -13156,17 +14673,30 @@
       <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="C11" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -13175,17 +14705,30 @@
       <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="C12" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -13194,17 +14737,30 @@
       <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="C13" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>2</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -13213,17 +14769,30 @@
       <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="C14" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="87" t="s">
+        <v>378</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -13232,17 +14801,30 @@
       <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="C15" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="87" t="s">
+        <v>379</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5">
+        <v>2</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -13251,17 +14833,30 @@
       <c r="B16" s="5">
         <v>12</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="C16" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="87" t="s">
+        <v>380</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2</v>
+      </c>
+      <c r="G16" s="5">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -13270,17 +14865,30 @@
       <c r="B17" s="5">
         <v>13</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="C17" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="87" t="s">
+        <v>381</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F17" s="5">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -13289,101 +14897,482 @@
       <c r="B18" s="5">
         <v>14</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="C18" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="87" t="s">
+        <v>382</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2</v>
+      </c>
+      <c r="G18" s="5">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="86" t="s">
+        <v>377</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="54" t="s">
+    <row r="19" spans="2:13" ht="24.75">
+      <c r="B19" s="5">
+        <v>15</v>
+      </c>
+      <c r="C19" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F19" s="5">
+        <v>3</v>
+      </c>
+      <c r="G19" s="5">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="86" t="s">
+        <v>377</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="2:13" s="27" customFormat="1" ht="30" customHeight="1">
+      <c r="B20" s="5">
+        <v>16</v>
+      </c>
+      <c r="C20" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="87" t="s">
+        <v>384</v>
+      </c>
+      <c r="E20" s="86" t="s">
+        <v>364</v>
+      </c>
+      <c r="F20" s="5">
+        <v>3</v>
+      </c>
+      <c r="G20" s="5">
+        <v>3</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="86" t="s">
+        <v>377</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="2:13" s="27" customFormat="1" ht="30" customHeight="1">
+      <c r="B21" s="5">
+        <v>17</v>
+      </c>
+      <c r="C21" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="87" t="s">
+        <v>385</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="F21" s="5">
+        <v>3</v>
+      </c>
+      <c r="G21" s="5">
+        <v>3</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="86" t="s">
+        <v>377</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="2:13" s="27" customFormat="1" ht="30" customHeight="1">
+      <c r="B22" s="5">
+        <v>18</v>
+      </c>
+      <c r="C22" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="87" t="s">
+        <v>386</v>
+      </c>
+      <c r="E22" s="86" t="s">
+        <v>388</v>
+      </c>
+      <c r="F22" s="5">
+        <v>3</v>
+      </c>
+      <c r="G22" s="5">
+        <v>3</v>
+      </c>
+      <c r="H22" s="5">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="86" t="s">
+        <v>377</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="2:13" s="27" customFormat="1" ht="30.75" customHeight="1">
+      <c r="B23" s="5">
+        <v>19</v>
+      </c>
+      <c r="C23" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E23" s="86" t="s">
+        <v>364</v>
+      </c>
+      <c r="F23" s="5">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5">
+        <v>3</v>
+      </c>
+      <c r="H23" s="5">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="86" t="s">
+        <v>377</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="2:13" s="27" customFormat="1" ht="30" customHeight="1">
+      <c r="B24" s="5">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="str">
+        <f t="shared" ref="H24:H26" si="0">IF(OR(F24="",G24=""),"",G24-F24+1)</f>
+        <v/>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="2:13" s="27" customFormat="1" ht="30" customHeight="1">
+      <c r="B25" s="5">
+        <v>21</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="2:13" s="27" customFormat="1" ht="30" customHeight="1">
+      <c r="B26" s="5">
+        <v>22</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="55"/>
-    </row>
-    <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="56" t="s">
+      <c r="C31" s="85"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="57"/>
-    </row>
-    <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="58" t="s">
+      <c r="C32" s="89"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="59"/>
-    </row>
-    <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="62" t="s">
+      <c r="C33" s="91"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+    </row>
+    <row r="34" spans="2:13">
+      <c r="B34" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="63"/>
-    </row>
-    <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="64" t="s">
+      <c r="C34" s="73"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+    </row>
+    <row r="35" spans="2:13">
+      <c r="B35" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="65"/>
-    </row>
-    <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="66" t="s">
+      <c r="C35" s="75"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="B36" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="67"/>
-    </row>
-    <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="68" t="s">
+      <c r="C36" s="77"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+    </row>
+    <row r="37" spans="2:13">
+      <c r="B37" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="69"/>
-    </row>
-    <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="70" t="s">
+      <c r="C37" s="79"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+    </row>
+    <row r="38" spans="2:13">
+      <c r="B38" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="71"/>
-    </row>
-    <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="60" t="s">
+      <c r="C38" s="81"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+    </row>
+    <row r="39" spans="2:13">
+      <c r="B39" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="61"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K19:M26">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(K$4&gt;=$F19,K$4&lt;=$G19)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C5:C18" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C5:C26" xr:uid="{F714CD52-3252-4A2F-A920-83116FF9A53B}">
       <formula1>"기획,설계,개발,배포,테스트,문서화,발표준비"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J5:J18" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J5:J26" xr:uid="{806793E7-B98D-4B99-9B67-E87FDE7A9C7A}">
       <formula1>"예정,진행중,완료"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -13407,16 +15396,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="39"/>
+      <c r="C2" s="52"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="30"/>
+      <c r="C3" s="43"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">
